--- a/panchang-data/Venice_Veneto2026.xlsx
+++ b/panchang-data/Venice_Veneto2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5418">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16279,6 +16279,9 @@
   </si>
   <si>
     <t>121°04'21.41</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16768,7 +16771,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16854,7 +16857,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16940,7 +16943,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -17026,7 +17029,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>90</v>
@@ -17112,7 +17115,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17198,7 +17201,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>127</v>
@@ -17284,7 +17287,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>144</v>
@@ -17370,7 +17373,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17456,7 +17459,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17542,7 +17545,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17628,7 +17631,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>90</v>
@@ -17714,7 +17717,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17800,7 +17803,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>127</v>
@@ -17886,7 +17889,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>144</v>
@@ -17972,7 +17975,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18058,7 +18061,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18144,7 +18147,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18230,7 +18233,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>90</v>
@@ -18316,7 +18319,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18402,7 +18405,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>127</v>
@@ -18488,7 +18491,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>144</v>
@@ -18574,7 +18577,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18660,7 +18663,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18746,7 +18749,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18832,7 +18835,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>90</v>
@@ -18918,7 +18921,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -19004,7 +19007,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>127</v>
@@ -19090,7 +19093,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>144</v>
@@ -19176,7 +19179,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19262,7 +19265,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19348,7 +19351,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19434,7 +19437,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>572</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>90</v>
@@ -19520,7 +19523,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19606,7 +19609,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>127</v>
@@ -19692,7 +19695,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>144</v>
@@ -19778,7 +19781,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19864,7 +19867,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19950,7 +19953,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -20036,7 +20039,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>90</v>
@@ -20122,7 +20125,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20208,7 +20211,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>127</v>
@@ -20294,7 +20297,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>144</v>
@@ -20380,7 +20383,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20466,7 +20469,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20552,7 +20555,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20638,7 +20641,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>90</v>
@@ -20724,7 +20727,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20810,7 +20813,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>127</v>
@@ -20896,7 +20899,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>144</v>
@@ -20982,7 +20985,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21068,7 +21071,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21154,7 +21157,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21240,7 +21243,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>90</v>
@@ -21326,7 +21329,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21412,7 +21415,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>127</v>
@@ -21498,7 +21501,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>144</v>
@@ -21584,7 +21587,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21670,7 +21673,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21756,7 +21759,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21842,7 +21845,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>90</v>
@@ -21928,7 +21931,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -22014,7 +22017,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>572</v>
+        <v>1014</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>127</v>
@@ -22100,7 +22103,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>144</v>
@@ -22186,7 +22189,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22272,7 +22275,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22358,7 +22361,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22444,7 +22447,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>90</v>
@@ -22530,7 +22533,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22616,7 +22619,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>127</v>
@@ -22702,7 +22705,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>144</v>
@@ -22788,7 +22791,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22874,7 +22877,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22960,7 +22963,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -23046,7 +23049,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>90</v>
@@ -23132,7 +23135,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23218,7 +23221,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>127</v>
@@ -23304,7 +23307,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>144</v>
@@ -23390,7 +23393,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23476,7 +23479,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23562,7 +23565,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23648,7 +23651,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>90</v>
@@ -23734,7 +23737,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23820,7 +23823,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>127</v>
@@ -23906,7 +23909,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>144</v>
@@ -23992,7 +23995,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24078,7 +24081,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24164,7 +24167,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24250,7 +24253,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>90</v>
@@ -24336,7 +24339,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24422,7 +24425,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>127</v>
@@ -24508,7 +24511,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1014</v>
+        <v>1439</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>144</v>
@@ -24594,7 +24597,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24680,7 +24683,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24766,7 +24769,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24852,7 +24855,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>90</v>
@@ -24938,7 +24941,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -25024,7 +25027,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>127</v>
@@ -25110,7 +25113,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>144</v>
@@ -25196,7 +25199,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25282,7 +25285,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25368,7 +25371,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25454,7 +25457,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>90</v>
@@ -25540,7 +25543,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25626,7 +25629,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>127</v>
@@ -25712,7 +25715,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>144</v>
@@ -25798,7 +25801,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25884,7 +25887,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25970,7 +25973,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -26056,7 +26059,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>90</v>
@@ -26142,7 +26145,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26228,7 +26231,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>127</v>
@@ -26314,7 +26317,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>144</v>
@@ -26400,7 +26403,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26486,7 +26489,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26572,7 +26575,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26658,7 +26661,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>90</v>
@@ -26744,7 +26747,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26830,7 +26833,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>127</v>
@@ -26916,7 +26919,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>144</v>
@@ -27002,7 +27005,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27088,7 +27091,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1439</v>
+        <v>1878</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27174,7 +27177,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27260,7 +27263,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>90</v>
@@ -27346,7 +27349,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27432,7 +27435,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>127</v>
@@ -27518,7 +27521,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>144</v>
@@ -27604,7 +27607,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27690,7 +27693,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27776,7 +27779,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27862,7 +27865,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>90</v>
@@ -27948,7 +27951,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -28034,7 +28037,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>127</v>
@@ -28120,7 +28123,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>144</v>
@@ -28206,7 +28209,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28292,7 +28295,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28378,7 +28381,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1878</v>
+        <v>2317</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28464,7 +28467,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>90</v>
@@ -28550,7 +28553,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28636,7 +28639,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>127</v>
@@ -28722,7 +28725,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>144</v>
@@ -28808,7 +28811,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28894,7 +28897,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28980,7 +28983,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29066,7 +29069,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>90</v>
@@ -29152,7 +29155,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29238,7 +29241,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>127</v>
@@ -29324,7 +29327,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>144</v>
@@ -29410,7 +29413,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29496,7 +29499,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29582,7 +29585,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29668,7 +29671,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1878</v>
+        <v>5417</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>90</v>
@@ -29754,7 +29757,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29840,7 +29843,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>127</v>
@@ -29926,7 +29929,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>144</v>
@@ -30012,7 +30015,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30098,7 +30101,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30184,7 +30187,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30270,7 +30273,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>90</v>
@@ -30356,7 +30359,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30442,7 +30445,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>127</v>
@@ -30528,7 +30531,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>144</v>
@@ -30614,7 +30617,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30700,7 +30703,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30786,7 +30789,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30872,7 +30875,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2317</v>
+        <v>5417</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>90</v>
